--- a/Report JSS 1B.xlsx
+++ b/Report JSS 1B.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonSetup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -19,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Report!$A$2:$N$57</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -2200,23 +2205,26 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2233,26 +2241,67 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2281,50 +2330,6 @@
     <xf numFmtId="49" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3490,7 +3495,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3581,7 +3586,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3677,7 +3682,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9278,14 +9283,14 @@
   <sheetData>
     <row r="1" spans="1:216">
       <c r="A1" s="42"/>
-      <c r="B1" s="235" t="s">
+      <c r="B1" s="224" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
+      <c r="C1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
       <c r="H1" s="49"/>
       <c r="I1" s="49"/>
       <c r="J1" s="50"/>
@@ -9294,28 +9299,28 @@
       <c r="M1" s="42"/>
       <c r="N1" s="56"/>
       <c r="O1" s="55"/>
-      <c r="P1" s="239" t="s">
+      <c r="P1" s="229" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="240"/>
-      <c r="R1" s="240"/>
-      <c r="S1" s="240"/>
-      <c r="T1" s="240"/>
-      <c r="U1" s="240"/>
-      <c r="V1" s="240"/>
+      <c r="Q1" s="230"/>
+      <c r="R1" s="230"/>
+      <c r="S1" s="230"/>
+      <c r="T1" s="230"/>
+      <c r="U1" s="230"/>
+      <c r="V1" s="230"/>
       <c r="W1" s="57"/>
       <c r="X1" s="57"/>
       <c r="Y1" s="54"/>
       <c r="Z1" s="75"/>
-      <c r="AA1" s="229" t="s">
+      <c r="AA1" s="225" t="s">
         <v>106</v>
       </c>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="229"/>
-      <c r="AD1" s="229"/>
-      <c r="AE1" s="229"/>
-      <c r="AF1" s="229"/>
-      <c r="AG1" s="229"/>
+      <c r="AB1" s="225"/>
+      <c r="AC1" s="225"/>
+      <c r="AD1" s="225"/>
+      <c r="AE1" s="225"/>
+      <c r="AF1" s="225"/>
+      <c r="AG1" s="225"/>
       <c r="AH1" s="75"/>
       <c r="AI1" s="75"/>
       <c r="AJ1" s="75"/>
@@ -9335,197 +9340,197 @@
       <c r="AV1" s="45"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="80"/>
-      <c r="AY1" s="236" t="s">
+      <c r="AY1" s="226" t="s">
         <v>93</v>
       </c>
-      <c r="AZ1" s="236"/>
-      <c r="BA1" s="236"/>
-      <c r="BB1" s="236"/>
-      <c r="BC1" s="236"/>
-      <c r="BD1" s="236"/>
-      <c r="BE1" s="236"/>
+      <c r="AZ1" s="226"/>
+      <c r="BA1" s="226"/>
+      <c r="BB1" s="226"/>
+      <c r="BC1" s="226"/>
+      <c r="BD1" s="226"/>
+      <c r="BE1" s="226"/>
       <c r="BF1" s="80"/>
       <c r="BG1" s="80"/>
       <c r="BH1" s="80"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="84"/>
-      <c r="BK1" s="237" t="s">
+      <c r="BK1" s="227" t="s">
         <v>64</v>
       </c>
-      <c r="BL1" s="238"/>
-      <c r="BM1" s="238"/>
-      <c r="BN1" s="238"/>
-      <c r="BO1" s="238"/>
-      <c r="BP1" s="238"/>
-      <c r="BQ1" s="238"/>
+      <c r="BL1" s="228"/>
+      <c r="BM1" s="228"/>
+      <c r="BN1" s="228"/>
+      <c r="BO1" s="228"/>
+      <c r="BP1" s="228"/>
+      <c r="BQ1" s="228"/>
       <c r="BR1" s="84"/>
       <c r="BS1" s="84"/>
       <c r="BT1" s="84"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="88"/>
-      <c r="BW1" s="230" t="s">
+      <c r="BW1" s="231" t="s">
         <v>87</v>
       </c>
-      <c r="BX1" s="230"/>
-      <c r="BY1" s="230"/>
-      <c r="BZ1" s="230"/>
-      <c r="CA1" s="230"/>
-      <c r="CB1" s="230"/>
-      <c r="CC1" s="230"/>
+      <c r="BX1" s="231"/>
+      <c r="BY1" s="231"/>
+      <c r="BZ1" s="231"/>
+      <c r="CA1" s="231"/>
+      <c r="CB1" s="231"/>
+      <c r="CC1" s="231"/>
       <c r="CD1" s="88"/>
       <c r="CE1" s="88"/>
       <c r="CF1" s="88"/>
       <c r="CG1" s="3"/>
       <c r="CH1" s="63"/>
-      <c r="CI1" s="231" t="s">
+      <c r="CI1" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="CJ1" s="231"/>
-      <c r="CK1" s="231"/>
-      <c r="CL1" s="231"/>
-      <c r="CM1" s="231"/>
-      <c r="CN1" s="231"/>
-      <c r="CO1" s="231"/>
+      <c r="CJ1" s="232"/>
+      <c r="CK1" s="232"/>
+      <c r="CL1" s="232"/>
+      <c r="CM1" s="232"/>
+      <c r="CN1" s="232"/>
+      <c r="CO1" s="232"/>
       <c r="CP1" s="63"/>
       <c r="CQ1" s="63"/>
       <c r="CR1" s="63"/>
       <c r="CS1" s="3"/>
       <c r="CT1" s="67"/>
-      <c r="CU1" s="232" t="s">
+      <c r="CU1" s="233" t="s">
         <v>67</v>
       </c>
-      <c r="CV1" s="232"/>
-      <c r="CW1" s="232"/>
-      <c r="CX1" s="232"/>
-      <c r="CY1" s="232"/>
-      <c r="CZ1" s="232"/>
-      <c r="DA1" s="232"/>
+      <c r="CV1" s="233"/>
+      <c r="CW1" s="233"/>
+      <c r="CX1" s="233"/>
+      <c r="CY1" s="233"/>
+      <c r="CZ1" s="233"/>
+      <c r="DA1" s="233"/>
       <c r="DB1" s="67"/>
       <c r="DC1" s="67"/>
       <c r="DD1" s="67"/>
       <c r="DE1" s="3"/>
       <c r="DF1" s="56"/>
-      <c r="DG1" s="233" t="s">
+      <c r="DG1" s="234" t="s">
         <v>89</v>
       </c>
-      <c r="DH1" s="233"/>
-      <c r="DI1" s="233"/>
-      <c r="DJ1" s="233"/>
-      <c r="DK1" s="233"/>
-      <c r="DL1" s="233"/>
-      <c r="DM1" s="233"/>
+      <c r="DH1" s="234"/>
+      <c r="DI1" s="234"/>
+      <c r="DJ1" s="234"/>
+      <c r="DK1" s="234"/>
+      <c r="DL1" s="234"/>
+      <c r="DM1" s="234"/>
       <c r="DN1" s="56"/>
       <c r="DO1" s="56"/>
       <c r="DP1" s="56"/>
       <c r="DQ1" s="3"/>
       <c r="DR1" s="96"/>
-      <c r="DS1" s="234" t="s">
+      <c r="DS1" s="235" t="s">
         <v>90</v>
       </c>
-      <c r="DT1" s="234"/>
-      <c r="DU1" s="234"/>
-      <c r="DV1" s="234"/>
-      <c r="DW1" s="234"/>
-      <c r="DX1" s="234"/>
-      <c r="DY1" s="234"/>
+      <c r="DT1" s="235"/>
+      <c r="DU1" s="235"/>
+      <c r="DV1" s="235"/>
+      <c r="DW1" s="235"/>
+      <c r="DX1" s="235"/>
+      <c r="DY1" s="235"/>
       <c r="DZ1" s="96"/>
       <c r="EA1" s="96"/>
       <c r="EB1" s="96"/>
       <c r="EC1" s="3"/>
       <c r="ED1" s="71"/>
-      <c r="EE1" s="226" t="s">
+      <c r="EE1" s="238" t="s">
         <v>65</v>
       </c>
-      <c r="EF1" s="226"/>
-      <c r="EG1" s="226"/>
-      <c r="EH1" s="226"/>
-      <c r="EI1" s="226"/>
-      <c r="EJ1" s="226"/>
-      <c r="EK1" s="226"/>
+      <c r="EF1" s="238"/>
+      <c r="EG1" s="238"/>
+      <c r="EH1" s="238"/>
+      <c r="EI1" s="238"/>
+      <c r="EJ1" s="238"/>
+      <c r="EK1" s="238"/>
       <c r="EL1" s="71"/>
       <c r="EM1" s="71"/>
       <c r="EN1" s="71"/>
       <c r="EO1" s="3"/>
       <c r="EP1" s="92"/>
-      <c r="EQ1" s="227" t="s">
+      <c r="EQ1" s="239" t="s">
         <v>68</v>
       </c>
-      <c r="ER1" s="227"/>
-      <c r="ES1" s="227"/>
-      <c r="ET1" s="227"/>
-      <c r="EU1" s="227"/>
-      <c r="EV1" s="227"/>
-      <c r="EW1" s="227"/>
+      <c r="ER1" s="239"/>
+      <c r="ES1" s="239"/>
+      <c r="ET1" s="239"/>
+      <c r="EU1" s="239"/>
+      <c r="EV1" s="239"/>
+      <c r="EW1" s="239"/>
       <c r="EX1" s="92"/>
       <c r="EY1" s="92"/>
       <c r="EZ1" s="92"/>
       <c r="FA1" s="3"/>
       <c r="FB1" s="105"/>
-      <c r="FC1" s="225" t="s">
+      <c r="FC1" s="237" t="s">
         <v>66</v>
       </c>
-      <c r="FD1" s="225"/>
-      <c r="FE1" s="225"/>
-      <c r="FF1" s="225"/>
-      <c r="FG1" s="225"/>
-      <c r="FH1" s="225"/>
-      <c r="FI1" s="225"/>
+      <c r="FD1" s="237"/>
+      <c r="FE1" s="237"/>
+      <c r="FF1" s="237"/>
+      <c r="FG1" s="237"/>
+      <c r="FH1" s="237"/>
+      <c r="FI1" s="237"/>
       <c r="FJ1" s="105"/>
       <c r="FK1" s="105"/>
       <c r="FL1" s="105"/>
       <c r="FM1" s="3"/>
       <c r="FN1" s="50"/>
-      <c r="FO1" s="228" t="s">
+      <c r="FO1" s="240" t="s">
         <v>94</v>
       </c>
-      <c r="FP1" s="228"/>
-      <c r="FQ1" s="228"/>
-      <c r="FR1" s="228"/>
-      <c r="FS1" s="228"/>
-      <c r="FT1" s="228"/>
-      <c r="FU1" s="228"/>
+      <c r="FP1" s="240"/>
+      <c r="FQ1" s="240"/>
+      <c r="FR1" s="240"/>
+      <c r="FS1" s="240"/>
+      <c r="FT1" s="240"/>
+      <c r="FU1" s="240"/>
       <c r="FV1" s="50"/>
       <c r="FW1" s="50"/>
       <c r="FX1" s="50"/>
       <c r="FY1" s="3"/>
       <c r="FZ1" s="75"/>
-      <c r="GA1" s="229" t="s">
+      <c r="GA1" s="225" t="s">
         <v>95</v>
       </c>
-      <c r="GB1" s="229"/>
-      <c r="GC1" s="229"/>
-      <c r="GD1" s="229"/>
-      <c r="GE1" s="229"/>
-      <c r="GF1" s="229"/>
-      <c r="GG1" s="229"/>
+      <c r="GB1" s="225"/>
+      <c r="GC1" s="225"/>
+      <c r="GD1" s="225"/>
+      <c r="GE1" s="225"/>
+      <c r="GF1" s="225"/>
+      <c r="GG1" s="225"/>
       <c r="GH1" s="75"/>
       <c r="GI1" s="75"/>
       <c r="GJ1" s="75"/>
       <c r="GK1" s="3"/>
       <c r="GL1" s="105"/>
-      <c r="GM1" s="225" t="s">
+      <c r="GM1" s="237" t="s">
         <v>63</v>
       </c>
-      <c r="GN1" s="225"/>
-      <c r="GO1" s="225"/>
-      <c r="GP1" s="225"/>
-      <c r="GQ1" s="225"/>
-      <c r="GR1" s="225"/>
-      <c r="GS1" s="225"/>
+      <c r="GN1" s="237"/>
+      <c r="GO1" s="237"/>
+      <c r="GP1" s="237"/>
+      <c r="GQ1" s="237"/>
+      <c r="GR1" s="237"/>
+      <c r="GS1" s="237"/>
       <c r="GT1" s="105"/>
       <c r="GU1" s="105"/>
       <c r="GV1" s="105"/>
       <c r="GW1" s="3"/>
       <c r="GX1" s="100"/>
-      <c r="GY1" s="224" t="s">
+      <c r="GY1" s="236" t="s">
         <v>83</v>
       </c>
-      <c r="GZ1" s="224"/>
-      <c r="HA1" s="224"/>
-      <c r="HB1" s="224"/>
-      <c r="HC1" s="224"/>
-      <c r="HD1" s="224"/>
-      <c r="HE1" s="224"/>
+      <c r="GZ1" s="236"/>
+      <c r="HA1" s="236"/>
+      <c r="HB1" s="236"/>
+      <c r="HC1" s="236"/>
+      <c r="HD1" s="236"/>
+      <c r="HE1" s="236"/>
       <c r="HF1" s="100"/>
       <c r="HG1" s="100"/>
       <c r="HH1" s="100"/>
@@ -12421,27 +12426,27 @@
         <v>110</v>
       </c>
       <c r="AM6" s="123">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN6" s="123">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AO6" s="123">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AP6" s="123">
         <v>10</v>
       </c>
       <c r="AQ6" s="45">
         <f t="shared" si="12"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR6" s="123">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="AS6" s="45">
         <f t="shared" si="13"/>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="45">
         <f t="shared" si="14"/>
@@ -13817,7 +13822,7 @@
       </c>
       <c r="V8" s="56">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W8" s="56" t="str">
         <f t="shared" si="7"/>
@@ -14602,28 +14607,28 @@
         <v>8</v>
       </c>
       <c r="AN9" s="123">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO9" s="123">
+        <v>2</v>
+      </c>
+      <c r="AP9" s="123">
         <v>8</v>
-      </c>
-      <c r="AP9" s="123">
-        <v>10</v>
       </c>
       <c r="AQ9" s="45">
         <f t="shared" si="12"/>
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AR9" s="123">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AS9" s="45">
         <f t="shared" si="13"/>
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="AT9" s="45">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AU9" s="45" t="str">
         <f t="shared" si="15"/>
@@ -15317,24 +15322,24 @@
         <v>5</v>
       </c>
       <c r="AN10" s="123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO10" s="123">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AP10" s="123">
         <v>10</v>
       </c>
       <c r="AQ10" s="45">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AR10" s="123">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="AS10" s="45">
         <f t="shared" si="13"/>
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AT10" s="45">
         <f t="shared" si="14"/>
@@ -15342,11 +15347,11 @@
       </c>
       <c r="AU10" s="45" t="str">
         <f t="shared" si="15"/>
-        <v>F</v>
+        <v>C</v>
       </c>
       <c r="AV10" s="45" t="str">
         <f t="shared" si="16"/>
-        <v>Fail</v>
+        <v>Credit</v>
       </c>
       <c r="AW10" s="3">
         <v>8</v>
@@ -18934,10 +18939,10 @@
         <v>119</v>
       </c>
       <c r="AM15" s="123">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN15" s="123">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AO15" s="123">
         <v>9</v>
@@ -18947,18 +18952,18 @@
       </c>
       <c r="AQ15" s="45">
         <f t="shared" si="12"/>
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AR15" s="123">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AS15" s="45">
         <f t="shared" si="13"/>
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AT15" s="45">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" s="45" t="str">
         <f t="shared" si="15"/>
@@ -19660,7 +19665,7 @@
         <v>120</v>
       </c>
       <c r="AM16" s="123">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN16" s="123">
         <v>6</v>
@@ -19673,26 +19678,26 @@
       </c>
       <c r="AQ16" s="45">
         <f t="shared" si="12"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AR16" s="123">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AS16" s="45">
         <f t="shared" si="13"/>
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="AT16" s="45">
         <f t="shared" si="14"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU16" s="45" t="str">
         <f t="shared" si="15"/>
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AV16" s="45" t="str">
         <f t="shared" si="16"/>
-        <v>Credit</v>
+        <v>Excellent</v>
       </c>
       <c r="AW16" s="3">
         <v>14</v>
@@ -23954,7 +23959,7 @@
       </c>
       <c r="V22" s="56">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W22" s="56" t="str">
         <f t="shared" si="7"/>
@@ -24010,39 +24015,39 @@
         <v>126</v>
       </c>
       <c r="AM22" s="123">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN22" s="123">
         <v>1</v>
       </c>
       <c r="AO22" s="123">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP22" s="123">
         <v>10</v>
       </c>
       <c r="AQ22" s="45">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AR22" s="123">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="AS22" s="45">
         <f t="shared" si="13"/>
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="AT22" s="45">
         <f t="shared" si="14"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU22" s="45" t="str">
         <f t="shared" si="15"/>
-        <v>P</v>
+        <v>A</v>
       </c>
       <c r="AV22" s="45" t="str">
         <f t="shared" si="16"/>
-        <v>Pass</v>
+        <v>Excellent</v>
       </c>
       <c r="AW22" s="3">
         <v>20</v>
@@ -27622,39 +27627,39 @@
         <v>131</v>
       </c>
       <c r="AM27" s="123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN27" s="123">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO27" s="123">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP27" s="123">
         <v>10</v>
       </c>
       <c r="AQ27" s="45">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AR27" s="123">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AS27" s="45">
         <f t="shared" si="13"/>
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AT27" s="45">
         <f t="shared" si="14"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU27" s="45" t="str">
         <f t="shared" si="15"/>
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AV27" s="45" t="str">
         <f t="shared" si="16"/>
-        <v>Credit</v>
+        <v>Excellent</v>
       </c>
       <c r="AW27" s="3">
         <v>25</v>
@@ -29736,23 +29741,23 @@
         <v>29</v>
       </c>
       <c r="T30" s="133">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="U30" s="56">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V30" s="56">
         <f t="shared" si="6"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W30" s="56" t="str">
         <f t="shared" si="7"/>
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="X30" s="56" t="str">
         <f t="shared" si="8"/>
-        <v>Credit</v>
+        <v>Excellent</v>
       </c>
       <c r="Y30" s="3">
         <v>28</v>
@@ -29800,39 +29805,39 @@
         <v>134</v>
       </c>
       <c r="AM30" s="123">
+        <v>7</v>
+      </c>
+      <c r="AN30" s="123">
         <v>5</v>
       </c>
-      <c r="AN30" s="123">
-        <v>2</v>
-      </c>
       <c r="AO30" s="123">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP30" s="123">
         <v>10</v>
       </c>
       <c r="AQ30" s="45">
         <f t="shared" si="12"/>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AR30" s="123">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AS30" s="45">
         <f t="shared" si="13"/>
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="AT30" s="45">
         <f t="shared" si="14"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AU30" s="45" t="str">
         <f t="shared" si="15"/>
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="AV30" s="45" t="str">
         <f t="shared" si="16"/>
-        <v>Credit</v>
+        <v>Excellent</v>
       </c>
       <c r="AW30" s="3">
         <v>28</v>
@@ -31252,31 +31257,31 @@
         <v>136</v>
       </c>
       <c r="AM32" s="123">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN32" s="123">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AO32" s="123">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP32" s="123">
         <v>10</v>
       </c>
       <c r="AQ32" s="45">
         <f t="shared" si="12"/>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AR32" s="123">
         <v>57</v>
       </c>
       <c r="AS32" s="45">
         <f t="shared" si="13"/>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AT32" s="45">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU32" s="45" t="str">
         <f t="shared" si="15"/>
@@ -33416,27 +33421,27 @@
         <v>139</v>
       </c>
       <c r="AM35" s="123">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AN35" s="123">
         <v>8</v>
       </c>
       <c r="AO35" s="123">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AP35" s="123">
         <v>10</v>
       </c>
       <c r="AQ35" s="45">
         <f t="shared" si="12"/>
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AR35" s="123">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AS35" s="45">
         <f t="shared" si="13"/>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AT35" s="45">
         <f t="shared" si="14"/>
@@ -37014,7 +37019,7 @@
         <v>144</v>
       </c>
       <c r="AM40" s="123">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AN40" s="123">
         <v>9</v>
@@ -37027,18 +37032,18 @@
       </c>
       <c r="AQ40" s="45">
         <f t="shared" si="12"/>
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AR40" s="123">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AS40" s="45">
         <f t="shared" si="13"/>
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AT40" s="45">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AU40" s="45" t="str">
         <f t="shared" si="15"/>
@@ -44366,16 +44371,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AY1:BE1"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="CI1:CO1"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="DG1:DM1"/>
-    <mergeCell ref="DS1:DY1"/>
     <mergeCell ref="GY1:HE1"/>
     <mergeCell ref="GM1:GS1"/>
     <mergeCell ref="EE1:EK1"/>
@@ -44383,6 +44378,16 @@
     <mergeCell ref="FC1:FI1"/>
     <mergeCell ref="FO1:FU1"/>
     <mergeCell ref="GA1:GG1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="CI1:CO1"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="DG1:DM1"/>
+    <mergeCell ref="DS1:DY1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AY1:BE1"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -44544,114 +44549,114 @@
       <c r="A10" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="275" t="str">
+      <c r="B10" s="241" t="str">
         <f>VLOOKUP(B14,Data!A1:I51,2,0)</f>
         <v>GAYAKARI ADATI PRAISE</v>
       </c>
-      <c r="C10" s="275"/>
-      <c r="D10" s="275"/>
-      <c r="E10" s="275"/>
-      <c r="F10" s="275"/>
-      <c r="G10" s="275"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
-      <c r="K10" s="273" t="s">
+      <c r="K10" s="242" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="273"/>
-      <c r="M10" s="275" t="str">
+      <c r="L10" s="242"/>
+      <c r="M10" s="241" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,7,0)</f>
         <v>2nd</v>
       </c>
-      <c r="N10" s="276"/>
+      <c r="N10" s="243"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="273">
+      <c r="B11" s="242">
         <f>VLOOKUP(B14,Data!A2:H51,4,0)</f>
         <v>10</v>
       </c>
-      <c r="C11" s="273"/>
-      <c r="D11" s="273"/>
-      <c r="E11" s="273"/>
-      <c r="F11" s="273"/>
-      <c r="G11" s="273"/>
+      <c r="C11" s="242"/>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
-      <c r="K11" s="273" t="s">
+      <c r="K11" s="242" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="273"/>
-      <c r="M11" s="275" t="str">
+      <c r="L11" s="242"/>
+      <c r="M11" s="241" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,3,0)</f>
         <v>JSS1B</v>
       </c>
-      <c r="N11" s="276"/>
+      <c r="N11" s="243"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="275" t="str">
+      <c r="B12" s="241" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,5,0)</f>
         <v>ADAMAWA</v>
       </c>
-      <c r="C12" s="275"/>
-      <c r="D12" s="275"/>
-      <c r="E12" s="275"/>
-      <c r="F12" s="275"/>
-      <c r="G12" s="275"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="241"/>
+      <c r="E12" s="241"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="273" t="s">
+      <c r="K12" s="242" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="273"/>
-      <c r="M12" s="275" t="str">
+      <c r="L12" s="242"/>
+      <c r="M12" s="241" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,8,0)</f>
         <v>16th January, 2026</v>
       </c>
-      <c r="N12" s="276"/>
+      <c r="N12" s="243"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="275" t="str">
+      <c r="B13" s="241" t="str">
         <f>VLOOKUP(B14,Data!A2:H51,6,0)</f>
         <v>HONG</v>
       </c>
-      <c r="C13" s="275"/>
-      <c r="D13" s="275"/>
-      <c r="E13" s="275"/>
-      <c r="F13" s="275"/>
-      <c r="G13" s="275"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
-      <c r="K13" s="273" t="s">
+      <c r="K13" s="242" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="273"/>
-      <c r="M13" s="275" t="str">
+      <c r="L13" s="242"/>
+      <c r="M13" s="241" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="276"/>
+      <c r="N13" s="243"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="273">
+      <c r="B14" s="242">
         <v>30</v>
       </c>
-      <c r="C14" s="273"/>
+      <c r="C14" s="242"/>
       <c r="D14" s="31"/>
       <c r="E14" s="31"/>
       <c r="F14" s="31"/>
@@ -44659,10 +44664,10 @@
       <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
-      <c r="K14" s="274"/>
-      <c r="L14" s="274"/>
-      <c r="M14" s="275"/>
-      <c r="N14" s="276"/>
+      <c r="K14" s="244"/>
+      <c r="L14" s="244"/>
+      <c r="M14" s="241"/>
+      <c r="N14" s="243"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="35" t="s">
@@ -44680,10 +44685,10 @@
       <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
-      <c r="K15" s="277"/>
-      <c r="L15" s="277"/>
-      <c r="M15" s="274"/>
-      <c r="N15" s="278"/>
+      <c r="K15" s="245"/>
+      <c r="L15" s="245"/>
+      <c r="M15" s="244"/>
+      <c r="N15" s="246"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="35" t="s">
@@ -44723,111 +44728,111 @@
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="244" t="s">
+      <c r="A18" s="270" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="246" t="s">
+      <c r="B18" s="272" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="246" t="s">
+      <c r="C18" s="272" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="246" t="s">
+      <c r="D18" s="272" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="246" t="s">
+      <c r="E18" s="272" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="248" t="s">
+      <c r="F18" s="274" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="246" t="s">
+      <c r="G18" s="272" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="246" t="s">
+      <c r="H18" s="272" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="248" t="s">
+      <c r="I18" s="274" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="250" t="s">
+      <c r="J18" s="276" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="265" t="s">
+      <c r="K18" s="247" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="266"/>
-      <c r="M18" s="267">
+      <c r="L18" s="248"/>
+      <c r="M18" s="249">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="268"/>
+      <c r="N18" s="250"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="245"/>
-      <c r="B19" s="247"/>
-      <c r="C19" s="247"/>
-      <c r="D19" s="247"/>
-      <c r="E19" s="247"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="247"/>
-      <c r="H19" s="247"/>
-      <c r="I19" s="249"/>
-      <c r="J19" s="251"/>
-      <c r="K19" s="269" t="s">
+      <c r="A19" s="271"/>
+      <c r="B19" s="273"/>
+      <c r="C19" s="273"/>
+      <c r="D19" s="273"/>
+      <c r="E19" s="273"/>
+      <c r="F19" s="275"/>
+      <c r="G19" s="273"/>
+      <c r="H19" s="273"/>
+      <c r="I19" s="275"/>
+      <c r="J19" s="277"/>
+      <c r="K19" s="251" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="270"/>
-      <c r="M19" s="257">
+      <c r="L19" s="252"/>
+      <c r="M19" s="253">
         <f>SUM(H23:H40)</f>
-        <v>1191</v>
-      </c>
-      <c r="N19" s="258"/>
+        <v>1189</v>
+      </c>
+      <c r="N19" s="254"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="245"/>
-      <c r="B20" s="247"/>
-      <c r="C20" s="247"/>
-      <c r="D20" s="247"/>
-      <c r="E20" s="247"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="247"/>
-      <c r="H20" s="247"/>
-      <c r="I20" s="249"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="269" t="s">
+      <c r="A20" s="271"/>
+      <c r="B20" s="273"/>
+      <c r="C20" s="273"/>
+      <c r="D20" s="273"/>
+      <c r="E20" s="273"/>
+      <c r="F20" s="275"/>
+      <c r="G20" s="273"/>
+      <c r="H20" s="273"/>
+      <c r="I20" s="275"/>
+      <c r="J20" s="277"/>
+      <c r="K20" s="251" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="270"/>
-      <c r="M20" s="271">
+      <c r="L20" s="252"/>
+      <c r="M20" s="255">
         <f>VLOOKUP(B14,Bsheet!A2:V51,21,0)</f>
-        <v>70.470588235294116</v>
-      </c>
-      <c r="N20" s="272"/>
+        <v>70.352941176470594</v>
+      </c>
+      <c r="N20" s="256"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="245"/>
-      <c r="B21" s="247"/>
-      <c r="C21" s="247"/>
-      <c r="D21" s="247"/>
-      <c r="E21" s="247"/>
-      <c r="F21" s="249"/>
-      <c r="G21" s="247"/>
-      <c r="H21" s="247"/>
-      <c r="I21" s="249"/>
-      <c r="J21" s="252"/>
-      <c r="K21" s="259" t="s">
+      <c r="A21" s="271"/>
+      <c r="B21" s="273"/>
+      <c r="C21" s="273"/>
+      <c r="D21" s="273"/>
+      <c r="E21" s="273"/>
+      <c r="F21" s="275"/>
+      <c r="G21" s="273"/>
+      <c r="H21" s="273"/>
+      <c r="I21" s="275"/>
+      <c r="J21" s="278"/>
+      <c r="K21" s="257" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="260"/>
-      <c r="M21" s="261">
+      <c r="L21" s="258"/>
+      <c r="M21" s="259">
         <f>VLOOKUP(B14,Bsheet!A2:V51,22,0)</f>
         <v>7</v>
       </c>
-      <c r="N21" s="262"/>
+      <c r="N21" s="260"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="245"/>
+      <c r="A22" s="271"/>
       <c r="B22" s="28" t="s">
         <v>58</v>
       </c>
@@ -44851,12 +44856,12 @@
       </c>
       <c r="I22" s="113"/>
       <c r="J22" s="114"/>
-      <c r="K22" s="263" t="s">
+      <c r="K22" s="261" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="263"/>
-      <c r="M22" s="263"/>
-      <c r="N22" s="264"/>
+      <c r="L22" s="261"/>
+      <c r="M22" s="261"/>
+      <c r="N22" s="262"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="29" t="s">
@@ -44898,13 +44903,13 @@
         <f>VLOOKUP(B14,Scoresheet!A3:K52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K23" s="256" t="str">
+      <c r="K23" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L23" s="257"/>
-      <c r="M23" s="257"/>
-      <c r="N23" s="258"/>
+      <c r="L23" s="253"/>
+      <c r="M23" s="253"/>
+      <c r="N23" s="254"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="29" t="s">
@@ -44946,13 +44951,13 @@
         <f>VLOOKUP(B14,Scoresheet!M3:W52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K24" s="256" t="str">
+      <c r="K24" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:X52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L24" s="257"/>
-      <c r="M24" s="257"/>
-      <c r="N24" s="258"/>
+      <c r="L24" s="253"/>
+      <c r="M24" s="253"/>
+      <c r="N24" s="254"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="29" t="s">
@@ -44994,13 +44999,13 @@
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K25" s="256" t="str">
+      <c r="K25" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AJ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L25" s="257"/>
-      <c r="M25" s="257"/>
-      <c r="N25" s="258"/>
+      <c r="L25" s="253"/>
+      <c r="M25" s="253"/>
+      <c r="N25" s="254"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="29" t="s">
@@ -45008,15 +45013,15 @@
       </c>
       <c r="B26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,3,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,4,0)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,5,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,6,0)</f>
@@ -45024,7 +45029,7 @@
       </c>
       <c r="F26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,7,0)</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,8,0)</f>
@@ -45032,23 +45037,23 @@
       </c>
       <c r="H26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,9,0)</f>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I26" s="27">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,10,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="27" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K26" s="256" t="str">
+      <c r="K26" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AV52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L26" s="257"/>
-      <c r="M26" s="257"/>
-      <c r="N26" s="258"/>
+      <c r="L26" s="253"/>
+      <c r="M26" s="253"/>
+      <c r="N26" s="254"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="29" t="s">
@@ -45090,13 +45095,13 @@
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K27" s="256" t="str">
+      <c r="K27" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BH52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L27" s="257"/>
-      <c r="M27" s="257"/>
-      <c r="N27" s="258"/>
+      <c r="L27" s="253"/>
+      <c r="M27" s="253"/>
+      <c r="N27" s="254"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="29" t="s">
@@ -45138,13 +45143,13 @@
         <f>VLOOKUP(B14,Scoresheet!BI3:BU52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K28" s="256" t="str">
+      <c r="K28" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BT52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L28" s="257"/>
-      <c r="M28" s="257"/>
-      <c r="N28" s="258"/>
+      <c r="L28" s="253"/>
+      <c r="M28" s="253"/>
+      <c r="N28" s="254"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="29" t="s">
@@ -45186,13 +45191,13 @@
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K29" s="256" t="str">
+      <c r="K29" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CF52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L29" s="257"/>
-      <c r="M29" s="257"/>
-      <c r="N29" s="258"/>
+      <c r="L29" s="253"/>
+      <c r="M29" s="253"/>
+      <c r="N29" s="254"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="29" t="s">
@@ -45234,13 +45239,13 @@
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K30" s="256" t="str">
+      <c r="K30" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CR52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L30" s="257"/>
-      <c r="M30" s="257"/>
-      <c r="N30" s="258"/>
+      <c r="L30" s="253"/>
+      <c r="M30" s="253"/>
+      <c r="N30" s="254"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="29" t="s">
@@ -45282,13 +45287,13 @@
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="256" t="str">
+      <c r="K31" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DD52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="257"/>
-      <c r="M31" s="257"/>
-      <c r="N31" s="258"/>
+      <c r="L31" s="253"/>
+      <c r="M31" s="253"/>
+      <c r="N31" s="254"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="29" t="s">
@@ -45330,13 +45335,13 @@
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="256" t="str">
+      <c r="K32" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DP52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="257"/>
-      <c r="M32" s="257"/>
-      <c r="N32" s="258"/>
+      <c r="L32" s="253"/>
+      <c r="M32" s="253"/>
+      <c r="N32" s="254"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="29" t="s">
@@ -45378,13 +45383,13 @@
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="256" t="str">
+      <c r="K33" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EB52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="257"/>
-      <c r="M33" s="257"/>
-      <c r="N33" s="258"/>
+      <c r="L33" s="253"/>
+      <c r="M33" s="253"/>
+      <c r="N33" s="254"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="29" t="s">
@@ -45426,13 +45431,13 @@
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K34" s="256" t="str">
+      <c r="K34" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EN52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L34" s="257"/>
-      <c r="M34" s="257"/>
-      <c r="N34" s="258"/>
+      <c r="L34" s="253"/>
+      <c r="M34" s="253"/>
+      <c r="N34" s="254"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="29" t="s">
@@ -45474,13 +45479,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K35" s="256" t="str">
+      <c r="K35" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EZ52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L35" s="257"/>
-      <c r="M35" s="257"/>
-      <c r="N35" s="258"/>
+      <c r="L35" s="253"/>
+      <c r="M35" s="253"/>
+      <c r="N35" s="254"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="29" t="s">
@@ -45522,13 +45527,13 @@
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,11,0)</f>
         <v>F</v>
       </c>
-      <c r="K36" s="256" t="str">
+      <c r="K36" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,12,0)</f>
         <v>Fail</v>
       </c>
-      <c r="L36" s="257"/>
-      <c r="M36" s="257"/>
-      <c r="N36" s="258"/>
+      <c r="L36" s="253"/>
+      <c r="M36" s="253"/>
+      <c r="N36" s="254"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="29" t="s">
@@ -45570,13 +45575,13 @@
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
         <v>C</v>
       </c>
-      <c r="K37" s="256" t="str">
+      <c r="K37" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM3:FX52,12,0)</f>
         <v>Credit</v>
       </c>
-      <c r="L37" s="257"/>
-      <c r="M37" s="257"/>
-      <c r="N37" s="258"/>
+      <c r="L37" s="253"/>
+      <c r="M37" s="253"/>
+      <c r="N37" s="254"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="29" t="s">
@@ -45618,13 +45623,13 @@
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K38" s="256" t="str">
+      <c r="K38" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GJ52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L38" s="257"/>
-      <c r="M38" s="257"/>
-      <c r="N38" s="258"/>
+      <c r="L38" s="253"/>
+      <c r="M38" s="253"/>
+      <c r="N38" s="254"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="29" t="s">
@@ -45666,13 +45671,13 @@
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K39" s="256" t="str">
+      <c r="K39" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GW52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L39" s="257"/>
-      <c r="M39" s="257"/>
-      <c r="N39" s="258"/>
+      <c r="L39" s="253"/>
+      <c r="M39" s="253"/>
+      <c r="N39" s="254"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="29" t="s">
@@ -45714,13 +45719,13 @@
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,11,0)</f>
         <v/>
       </c>
-      <c r="K40" s="256" t="str">
+      <c r="K40" s="263" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,12,0)</f>
         <v/>
       </c>
-      <c r="L40" s="257"/>
-      <c r="M40" s="257"/>
-      <c r="N40" s="258"/>
+      <c r="L40" s="253"/>
+      <c r="M40" s="253"/>
+      <c r="N40" s="254"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="22"/>
@@ -45744,20 +45749,20 @@
       </c>
       <c r="B42" s="37"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="254" t="s">
+      <c r="D42" s="264" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="254"/>
+      <c r="E42" s="264"/>
       <c r="F42" s="39"/>
       <c r="G42" s="40"/>
-      <c r="H42" s="255" t="s">
+      <c r="H42" s="265" t="s">
         <v>72</v>
       </c>
-      <c r="I42" s="255"/>
-      <c r="J42" s="255"/>
-      <c r="K42" s="255"/>
-      <c r="L42" s="255"/>
-      <c r="M42" s="255"/>
+      <c r="I42" s="265"/>
+      <c r="J42" s="265"/>
+      <c r="K42" s="265"/>
+      <c r="L42" s="265"/>
+      <c r="M42" s="265"/>
       <c r="N42" s="41"/>
       <c r="O42" s="17"/>
     </row>
@@ -45770,23 +45775,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="254" t="s">
+      <c r="D43" s="264" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="254"/>
+      <c r="E43" s="264"/>
       <c r="F43" s="39">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>3</v>
       </c>
       <c r="G43" s="40"/>
-      <c r="H43" s="255" t="s">
+      <c r="H43" s="265" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="255"/>
-      <c r="J43" s="255"/>
-      <c r="K43" s="255"/>
-      <c r="L43" s="255"/>
-      <c r="M43" s="255"/>
+      <c r="I43" s="265"/>
+      <c r="J43" s="265"/>
+      <c r="K43" s="265"/>
+      <c r="L43" s="265"/>
+      <c r="M43" s="265"/>
       <c r="N43" s="41"/>
       <c r="O43" s="17"/>
     </row>
@@ -45799,23 +45804,23 @@
         <v>3</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="254" t="s">
+      <c r="D44" s="264" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="254"/>
+      <c r="E44" s="264"/>
       <c r="F44" s="39">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>3</v>
       </c>
       <c r="G44" s="40"/>
-      <c r="H44" s="255" t="s">
+      <c r="H44" s="265" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="255"/>
-      <c r="J44" s="255"/>
-      <c r="K44" s="255"/>
-      <c r="L44" s="255"/>
-      <c r="M44" s="255"/>
+      <c r="I44" s="265"/>
+      <c r="J44" s="265"/>
+      <c r="K44" s="265"/>
+      <c r="L44" s="265"/>
+      <c r="M44" s="265"/>
       <c r="N44" s="41"/>
       <c r="O44" s="17"/>
     </row>
@@ -45828,23 +45833,23 @@
         <v>3</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="254" t="s">
+      <c r="D45" s="264" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="254"/>
+      <c r="E45" s="264"/>
       <c r="F45" s="39">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>3</v>
       </c>
       <c r="G45" s="40"/>
-      <c r="H45" s="255" t="s">
+      <c r="H45" s="265" t="s">
         <v>75</v>
       </c>
-      <c r="I45" s="255"/>
-      <c r="J45" s="255"/>
-      <c r="K45" s="255"/>
-      <c r="L45" s="255"/>
-      <c r="M45" s="255"/>
+      <c r="I45" s="265"/>
+      <c r="J45" s="265"/>
+      <c r="K45" s="265"/>
+      <c r="L45" s="265"/>
+      <c r="M45" s="265"/>
       <c r="N45" s="41"/>
       <c r="O45" s="17"/>
     </row>
@@ -45857,23 +45862,23 @@
         <v>3</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="254" t="s">
+      <c r="D46" s="264" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="254"/>
+      <c r="E46" s="264"/>
       <c r="F46" s="39">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>3</v>
       </c>
       <c r="G46" s="40"/>
-      <c r="H46" s="255" t="s">
+      <c r="H46" s="265" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="255"/>
-      <c r="J46" s="255"/>
-      <c r="K46" s="255"/>
-      <c r="L46" s="255"/>
-      <c r="M46" s="255"/>
+      <c r="I46" s="265"/>
+      <c r="J46" s="265"/>
+      <c r="K46" s="265"/>
+      <c r="L46" s="265"/>
+      <c r="M46" s="265"/>
       <c r="N46" s="41"/>
       <c r="O46" s="17"/>
     </row>
@@ -45886,23 +45891,23 @@
         <v>3</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="254" t="s">
+      <c r="D47" s="264" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="254"/>
+      <c r="E47" s="264"/>
       <c r="F47" s="39">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="40"/>
-      <c r="H47" s="255" t="s">
+      <c r="H47" s="265" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="255"/>
-      <c r="J47" s="255"/>
-      <c r="K47" s="255"/>
-      <c r="L47" s="255"/>
-      <c r="M47" s="255"/>
+      <c r="I47" s="265"/>
+      <c r="J47" s="265"/>
+      <c r="K47" s="265"/>
+      <c r="L47" s="265"/>
+      <c r="M47" s="265"/>
       <c r="N47" s="41"/>
       <c r="O47" s="17"/>
     </row>
@@ -46007,11 +46012,11 @@
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="241" t="s">
+      <c r="A53" s="266" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="242"/>
-      <c r="C53" s="242"/>
+      <c r="B53" s="267"/>
+      <c r="C53" s="267"/>
       <c r="D53" s="17" t="s">
         <v>79</v>
       </c>
@@ -46029,16 +46034,16 @@
       <c r="M53" s="17"/>
       <c r="N53" s="16"/>
       <c r="O53" s="17"/>
-      <c r="R53" s="243"/>
-      <c r="S53" s="243"/>
-      <c r="T53" s="243"/>
+      <c r="R53" s="269"/>
+      <c r="S53" s="269"/>
+      <c r="T53" s="269"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="241" t="s">
+      <c r="A54" s="266" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="242"/>
-      <c r="C54" s="242"/>
+      <c r="B54" s="267"/>
+      <c r="C54" s="267"/>
       <c r="D54" s="17" t="s">
         <v>79</v>
       </c>
@@ -46053,43 +46058,43 @@
       <c r="M54" s="17"/>
       <c r="N54" s="16"/>
       <c r="O54" s="17"/>
-      <c r="R54" s="243"/>
-      <c r="S54" s="243"/>
-      <c r="T54" s="243"/>
+      <c r="R54" s="269"/>
+      <c r="S54" s="269"/>
+      <c r="T54" s="269"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="241" t="s">
+      <c r="A55" s="266" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="242"/>
-      <c r="C55" s="242"/>
+      <c r="B55" s="267"/>
+      <c r="C55" s="267"/>
       <c r="D55" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="253" t="str">
+      <c r="E55" s="268" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="253"/>
-      <c r="G55" s="253"/>
-      <c r="H55" s="253"/>
-      <c r="I55" s="253"/>
-      <c r="J55" s="253"/>
+      <c r="F55" s="268"/>
+      <c r="G55" s="268"/>
+      <c r="H55" s="268"/>
+      <c r="I55" s="268"/>
+      <c r="J55" s="268"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" s="16"/>
       <c r="O55" s="17"/>
-      <c r="R55" s="243"/>
-      <c r="S55" s="243"/>
-      <c r="T55" s="243"/>
+      <c r="R55" s="269"/>
+      <c r="S55" s="269"/>
+      <c r="T55" s="269"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="241" t="s">
+      <c r="A56" s="266" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="242"/>
-      <c r="C56" s="242"/>
+      <c r="B56" s="267"/>
+      <c r="C56" s="267"/>
       <c r="D56" s="17" t="s">
         <v>79</v>
       </c>
@@ -46107,9 +46112,9 @@
       <c r="M56" s="17"/>
       <c r="N56" s="16"/>
       <c r="O56" s="17"/>
-      <c r="R56" s="243"/>
-      <c r="S56" s="243"/>
-      <c r="T56" s="243"/>
+      <c r="R56" s="269"/>
+      <c r="S56" s="269"/>
+      <c r="T56" s="269"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="24"/>
@@ -46146,65 +46151,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -46221,6 +46167,65 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -47883,7 +47888,7 @@
     <col min="21" max="22" width="11.28515625" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="75">
+    <row r="1" spans="1:22" ht="74.25">
       <c r="A1" s="176" t="s">
         <v>172</v>
       </c>
@@ -48236,7 +48241,7 @@
       </c>
       <c r="E5" s="3">
         <f>Scoresheet!AS6</f>
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F5" s="3">
         <f>Scoresheet!BE6</f>
@@ -48296,11 +48301,11 @@
       </c>
       <c r="T5" s="3">
         <f t="shared" si="0"/>
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="U5" s="112">
         <f t="shared" si="1"/>
-        <v>72.647058823529406</v>
+        <v>73.17647058823529</v>
       </c>
       <c r="V5" s="183">
         <f t="shared" si="2"/>
@@ -48503,7 +48508,7 @@
       </c>
       <c r="E8" s="3">
         <f>Scoresheet!AS9</f>
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3">
         <f>Scoresheet!BE9</f>
@@ -48563,15 +48568,15 @@
       </c>
       <c r="T8" s="3">
         <f t="shared" si="0"/>
-        <v>1117</v>
+        <v>1101</v>
       </c>
       <c r="U8" s="112">
         <f t="shared" si="1"/>
-        <v>65.705882352941174</v>
+        <v>64.764705882352942</v>
       </c>
       <c r="V8" s="183">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -48592,7 +48597,7 @@
       </c>
       <c r="E9" s="3">
         <f>Scoresheet!AS10</f>
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3">
         <f>Scoresheet!BE10</f>
@@ -48652,11 +48657,11 @@
       </c>
       <c r="T9" s="3">
         <f t="shared" si="0"/>
-        <v>646</v>
+        <v>668</v>
       </c>
       <c r="U9" s="112">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>39.294117647058826</v>
       </c>
       <c r="V9" s="183">
         <f t="shared" si="2"/>
@@ -49037,7 +49042,7 @@
       </c>
       <c r="E14" s="3">
         <f>Scoresheet!AS15</f>
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14" s="3">
         <f>Scoresheet!BE15</f>
@@ -49097,11 +49102,11 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="0"/>
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="U14" s="112">
         <f t="shared" si="1"/>
-        <v>84.588235294117652</v>
+        <v>84.470588235294116</v>
       </c>
       <c r="V14" s="183">
         <f t="shared" si="2"/>
@@ -49126,7 +49131,7 @@
       </c>
       <c r="E15" s="3">
         <f>Scoresheet!AS16</f>
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="F15" s="3">
         <f>Scoresheet!BE16</f>
@@ -49186,15 +49191,15 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="0"/>
-        <v>1086</v>
+        <v>1103</v>
       </c>
       <c r="U15" s="112">
         <f t="shared" si="1"/>
-        <v>63.882352941176471</v>
+        <v>64.882352941176464</v>
       </c>
       <c r="V15" s="183">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -49660,7 +49665,7 @@
       </c>
       <c r="E21" s="3">
         <f>Scoresheet!AS22</f>
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="F21" s="3">
         <f>Scoresheet!BE22</f>
@@ -49720,15 +49725,15 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="0"/>
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="U21" s="112">
         <f t="shared" si="1"/>
-        <v>52.117647058823529</v>
+        <v>53.705882352941174</v>
       </c>
       <c r="V21" s="183">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -49906,7 +49911,7 @@
       </c>
       <c r="V23" s="183">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -50105,7 +50110,7 @@
       </c>
       <c r="E26" s="3">
         <f>Scoresheet!AS27</f>
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F26" s="3">
         <f>Scoresheet!BE27</f>
@@ -50165,11 +50170,11 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="0"/>
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="U26" s="112">
         <f t="shared" si="1"/>
-        <v>50.470588235294116</v>
+        <v>51.352941176470587</v>
       </c>
       <c r="V26" s="183">
         <f t="shared" si="2"/>
@@ -50364,7 +50369,7 @@
       </c>
       <c r="C29" s="3">
         <f>Scoresheet!U30</f>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D29" s="3">
         <f>Scoresheet!AG30</f>
@@ -50372,7 +50377,7 @@
       </c>
       <c r="E29" s="3">
         <f>Scoresheet!AS30</f>
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F29" s="3">
         <f>Scoresheet!BE30</f>
@@ -50432,11 +50437,11 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="0"/>
-        <v>1126</v>
+        <v>1146</v>
       </c>
       <c r="U29" s="112">
         <f t="shared" si="1"/>
-        <v>66.235294117647058</v>
+        <v>67.411764705882348</v>
       </c>
       <c r="V29" s="183">
         <f t="shared" si="2"/>
@@ -50529,7 +50534,7 @@
       </c>
       <c r="V30" s="183">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -50550,7 +50555,7 @@
       </c>
       <c r="E31" s="3">
         <f>Scoresheet!AS32</f>
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F31" s="3">
         <f>Scoresheet!BE32</f>
@@ -50610,11 +50615,11 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="0"/>
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="U31" s="112">
         <f t="shared" si="1"/>
-        <v>70.470588235294116</v>
+        <v>70.352941176470594</v>
       </c>
       <c r="V31" s="183">
         <f t="shared" si="2"/>
@@ -50817,7 +50822,7 @@
       </c>
       <c r="E34" s="3">
         <f>Scoresheet!AS35</f>
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F34" s="3">
         <f>Scoresheet!BE35</f>
@@ -50877,11 +50882,11 @@
       </c>
       <c r="T34" s="3">
         <f t="shared" si="0"/>
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="U34" s="112">
         <f t="shared" si="1"/>
-        <v>77.529411764705884</v>
+        <v>77.411764705882348</v>
       </c>
       <c r="V34" s="183">
         <f t="shared" si="2"/>
@@ -51262,7 +51267,7 @@
       </c>
       <c r="E39" s="3">
         <f>Scoresheet!AS40</f>
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="F39" s="3">
         <f>Scoresheet!BE40</f>
@@ -51322,11 +51327,11 @@
       </c>
       <c r="T39" s="3">
         <f t="shared" si="0"/>
-        <v>1158</v>
+        <v>1179</v>
       </c>
       <c r="U39" s="112">
         <f t="shared" si="1"/>
-        <v>68.117647058823536</v>
+        <v>69.352941176470594</v>
       </c>
       <c r="V39" s="183">
         <f t="shared" si="2"/>
@@ -51419,7 +51424,7 @@
       </c>
       <c r="V40" s="183">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:22">
